--- a/data/trans_camb/IP16A05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 32,88</t>
+          <t>1,71; 32,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 4,65</t>
+          <t>-12,92; 4,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 13,98</t>
+          <t>-8,23; 13,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 15,9</t>
+          <t>-11,43; 15,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 21,34</t>
+          <t>-10,19; 21,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 0,0</t>
+          <t>-22,03; -0,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 20,46</t>
+          <t>-1,33; 19,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 10,83</t>
+          <t>-8,21; 10,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 3,35</t>
+          <t>-11,94; 3,51</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 1610,35</t>
+          <t>-15,7; 1537,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,08; 282,79</t>
+          <t>-66,69; 331,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,13; 388,09</t>
+          <t>-70,34; 489,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 476,98</t>
+          <t>-15,19; 466,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,87; 234,36</t>
+          <t>-70,37; 203,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-89,77; 93,84</t>
+          <t>-87,49; 112,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 14,7</t>
+          <t>-9,61; 15,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 15,93</t>
+          <t>-7,75; 15,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 4,74</t>
+          <t>-14,44; 5,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 22,03</t>
+          <t>-3,11; 21,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 10,81</t>
+          <t>-8,77; 10,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 8,9</t>
+          <t>-10,17; 8,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 14,63</t>
+          <t>-2,58; 15,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 11,19</t>
+          <t>-5,24; 9,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 4,54</t>
+          <t>-9,0; 4,78</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,1; 230,51</t>
+          <t>-53,63; 237,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 232,18</t>
+          <t>-44,71; 263,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,26; 93,73</t>
+          <t>-80,61; 96,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 538,92</t>
+          <t>-43,8; 558,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,17; 313,6</t>
+          <t>-79,43; 349,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,85; 299,26</t>
+          <t>-78,25; 283,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 228,53</t>
+          <t>-22,72; 235,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,8; 171,73</t>
+          <t>-38,93; 149,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,67; 75,6</t>
+          <t>-66,17; 78,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 21,87</t>
+          <t>-3,1; 22,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 15,87</t>
+          <t>-7,86; 16,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 15,78</t>
+          <t>-9,31; 18,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 5,48</t>
+          <t>-15,53; 5,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 25,78</t>
+          <t>-3,32; 26,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 4,86</t>
+          <t>-14,8; 4,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 9,85</t>
+          <t>-7,14; 9,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 16,88</t>
+          <t>-2,69; 16,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 7,99</t>
+          <t>-9,13; 8,31</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,68; inf</t>
+          <t>-37,26; 863,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,35; 646,85</t>
+          <t>-79,91; 717,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,8; 729,19</t>
+          <t>-71,49; 808,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-91,42; 164,36</t>
+          <t>-91,23; 119,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 533,02</t>
+          <t>-27,01; 522,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,76; 150,73</t>
+          <t>-88,81; 142,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,74; 186,58</t>
+          <t>-51,38; 188,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 292,47</t>
+          <t>-29,02; 299,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,04; 153,63</t>
+          <t>-69,92; 142,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 24,42</t>
+          <t>-5,42; 25,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 18,1</t>
+          <t>-9,71; 16,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 6,22</t>
+          <t>-16,19; 6,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 12,86</t>
+          <t>-10,82; 13,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 10,39</t>
+          <t>-13,19; 10,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -1,12</t>
+          <t>-19,44; -0,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 14,74</t>
+          <t>-3,75; 14,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 10,35</t>
+          <t>-7,89; 10,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -0,02</t>
+          <t>-13,68; 0,4</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,15; inf</t>
+          <t>-38,05; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-72,94; —</t>
+          <t>-74,54; 600,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,04; 261,53</t>
+          <t>-65,86; 231,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-83,51; 207,75</t>
+          <t>-85,01; 223,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 144,43</t>
+          <t>-100,0; 71,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 248,56</t>
+          <t>-27,84; 274,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-56,5; 191,14</t>
+          <t>-59,48; 165,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-91,67; 24,56</t>
+          <t>-92,5; 23,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,11; 16,15</t>
+          <t>2,5; 15,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 8,48</t>
+          <t>-3,03; 8,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 6,73</t>
+          <t>-6,73; 5,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 8,73</t>
+          <t>-2,53; 8,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 9,33</t>
+          <t>-3,49; 9,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 0,54</t>
+          <t>-9,99; -0,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 10,34</t>
+          <t>1,26; 10,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 7,19</t>
+          <t>-1,55; 7,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 1,67</t>
+          <t>-6,83; 1,1</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>16,17; 285,28</t>
+          <t>17,39; 254,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 135,96</t>
+          <t>-30,02; 137,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 105,53</t>
+          <t>-56,81; 95,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 118,08</t>
+          <t>-22,38; 119,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,1; 122,12</t>
+          <t>-29,68; 129,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,9; 10,21</t>
+          <t>-73,84; 5,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,21; 140,88</t>
+          <t>9,42; 126,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 93,45</t>
+          <t>-13,15; 90,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 20,49</t>
+          <t>-57,69; 16,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 32,64</t>
+          <t>-0,34; 30,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 4,21</t>
+          <t>-12,83; 3,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 13,17</t>
+          <t>-9,98; 12,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 15,67</t>
+          <t>-10,99; 16,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 21,75</t>
+          <t>-10,92; 20,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -0,52</t>
+          <t>-22,4; -0,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 19,67</t>
+          <t>-1,46; 19,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 10,51</t>
+          <t>-8,53; 10,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 3,51</t>
+          <t>-11,94; 2,96</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 1537,3</t>
+          <t>-34,21; 1460,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,69; 331,2</t>
+          <t>-64,77; 388,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,34; 489,42</t>
+          <t>-68,34; 540,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 220,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 466,64</t>
+          <t>-19,29; 402,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,37; 203,72</t>
+          <t>-72,23; 188,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,49; 112,38</t>
+          <t>-87,66; 107,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 15,67</t>
+          <t>-9,15; 14,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 15,66</t>
+          <t>-7,83; 15,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 5,71</t>
+          <t>-14,67; 5,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 21,33</t>
+          <t>-1,76; 22,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 10,95</t>
+          <t>-8,6; 11,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 8,27</t>
+          <t>-8,96; 8,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 15,38</t>
+          <t>-2,21; 15,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 9,55</t>
+          <t>-4,44; 10,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 4,78</t>
+          <t>-8,86; 5,3</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,63; 237,05</t>
+          <t>-58,22; 213,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,71; 263,75</t>
+          <t>-46,21; 243,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,61; 96,66</t>
+          <t>-79,64; 81,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,8; 558,56</t>
+          <t>-27,7; 672,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,43; 349,95</t>
+          <t>-80,23; 391,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 283,63</t>
+          <t>-73,59; 296,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 235,31</t>
+          <t>-22,82; 225,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,93; 149,76</t>
+          <t>-34,39; 151,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,17; 78,89</t>
+          <t>-66,97; 92,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 22,11</t>
+          <t>-4,17; 21,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 16,16</t>
+          <t>-7,92; 16,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 18,0</t>
+          <t>-10,58; 17,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 5,41</t>
+          <t>-16,72; 4,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 26,44</t>
+          <t>-3,09; 25,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 4,69</t>
+          <t>-15,37; 4,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 9,62</t>
+          <t>-7,07; 9,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 16,26</t>
+          <t>-3,73; 16,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 8,31</t>
+          <t>-9,18; 7,82</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,26; 863,17</t>
+          <t>-48,59; 889,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,91; 717,27</t>
+          <t>-71,75; inf</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,49; 808,97</t>
+          <t>-80,23; 1212,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-91,23; 119,9</t>
+          <t>-88,93; 181,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 522,18</t>
+          <t>-32,75; 505,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,81; 142,82</t>
+          <t>-87,0; 163,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-51,38; 188,05</t>
+          <t>-52,26; 163,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 299,4</t>
+          <t>-29,1; 285,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,92; 142,15</t>
+          <t>-67,86; 146,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 25,0</t>
+          <t>-3,76; 24,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 16,38</t>
+          <t>-9,64; 16,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 6,71</t>
+          <t>-16,78; 6,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 13,25</t>
+          <t>-9,34; 13,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 10,02</t>
+          <t>-12,3; 11,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,44; -0,99</t>
+          <t>-18,31; -1,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 14,75</t>
+          <t>-2,43; 16,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 10,01</t>
+          <t>-7,57; 10,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 0,4</t>
+          <t>-14,5; 0,44</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,05; —</t>
+          <t>-38,43; 881,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,54; 600,48</t>
+          <t>-73,13; 649,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-65,86; 231,0</t>
+          <t>-58,44; 248,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-85,01; 223,39</t>
+          <t>-81,76; 253,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 71,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,84; 274,93</t>
+          <t>-20,71; 304,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,48; 165,76</t>
+          <t>-53,19; 234,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-92,5; 23,18</t>
+          <t>-92,6; 21,12</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,5; 15,44</t>
+          <t>2,68; 15,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 8,47</t>
+          <t>-3,51; 8,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 5,75</t>
+          <t>-6,47; 5,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 8,82</t>
+          <t>-2,99; 9,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 9,57</t>
+          <t>-3,26; 9,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,99; -0,26</t>
+          <t>-10,03; -0,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,12</t>
+          <t>0,93; 10,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 7,01</t>
+          <t>-1,34; 7,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 1,1</t>
+          <t>-6,87; 1,12</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17,39; 254,07</t>
+          <t>19,25; 250,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 137,43</t>
+          <t>-31,27; 129,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,81; 95,67</t>
+          <t>-59,12; 90,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 119,51</t>
+          <t>-24,43; 117,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 129,07</t>
+          <t>-27,93; 122,51</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-73,84; 5,15</t>
+          <t>-75,81; 3,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,42; 126,76</t>
+          <t>7,04; 139,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 90,77</t>
+          <t>-13,16; 88,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-57,69; 16,73</t>
+          <t>-57,68; 17,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A05-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumieron medicamentos antibióticos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,28</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-9,36</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>15,39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-3,79</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,28</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,58</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,02</t>
+          <t>-3,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 30,96</t>
+          <t>-12,99; 15,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 3,61</t>
+          <t>-10,42; 21,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 12,32</t>
+          <t>-21,53; 0,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 16,34</t>
+          <t>1,64; 32,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 20,97</t>
+          <t>-12,27; 4,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,4; -0,13</t>
+          <t>-8,35; 13,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 19,41</t>
+          <t>-0,13; 20,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 10,63</t>
+          <t>-8,23; 10,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 2,96</t>
+          <t>-11,75; 3,62</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23,21%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36,21%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-79,11%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>245,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-60,41%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23,21%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,21%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-81,02%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-45,36%</t>
+          <t>-43,57%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 1460,18</t>
+          <t>-66,08; 282,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-73,13; 388,09</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-18,4; 1610,35</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-64,77; 388,76</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-68,34; 540,28</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 220,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 402,6</t>
+          <t>-10,1; 476,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,23; 188,91</t>
+          <t>-67,87; 234,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,66; 107,72</t>
+          <t>-89,34; 117,36</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,88</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,36</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,29</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,7</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-3,7</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>-1,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 14,97</t>
+          <t>-1,49; 22,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 15,21</t>
+          <t>-9,3; 10,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 5,14</t>
+          <t>-8,63; 9,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 22,88</t>
+          <t>-8,51; 14,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 11,7</t>
+          <t>-7,57; 15,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 8,78</t>
+          <t>-14,14; 6,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 15,2</t>
+          <t>-2,78; 14,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 10,32</t>
+          <t>-5,28; 11,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 5,3</t>
+          <t>-8,25; 5,41</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>123,58%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>17,47%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>34,88%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-35,95%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>123,58%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-0,99%</t>
+          <t>-30,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-22,49%</t>
+          <t>-17,08%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,22; 213,3</t>
+          <t>-32,88; 538,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,21; 243,63</t>
+          <t>-82,17; 313,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,64; 81,65</t>
+          <t>-72,63; 320,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 672,73</t>
+          <t>-56,1; 230,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,23; 391,24</t>
+          <t>-47,24; 232,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,59; 296,26</t>
+          <t>-76,89; 108,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 225,51</t>
+          <t>-21,72; 228,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 151,72</t>
+          <t>-40,8; 171,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,97; 92,19</t>
+          <t>-64,63; 92,25</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,67</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,94</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-5,07</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>9,48</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,71</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,05</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,67</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,94</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,88</t>
+          <t>3,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-1,37</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 21,02</t>
+          <t>-15,87; 5,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 16,04</t>
+          <t>-2,73; 25,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 17,01</t>
+          <t>-15,69; 4,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 4,78</t>
+          <t>-3,62; 21,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 25,17</t>
+          <t>-8,94; 15,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 4,93</t>
+          <t>-8,21; 12,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 9,8</t>
+          <t>-5,95; 9,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 16,03</t>
+          <t>-2,93; 16,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 7,82</t>
+          <t>-9,66; 5,23</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-42,42%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-46,03%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>132,21%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>51,7%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>42,54%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-42,42%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-44,28%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-9,85%</t>
+          <t>-14,54%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,59; 889,39</t>
+          <t>-91,42; 164,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,75; inf</t>
+          <t>-27,68; 533,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,23; 1212,09</t>
+          <t>-88,7; 148,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-88,93; 181,16</t>
+          <t>-40,68; inf</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,75; 505,61</t>
+          <t>-77,35; 646,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,0; 163,86</t>
+          <t>-65,91; 608,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 163,42</t>
+          <t>-48,74; 186,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 285,62</t>
+          <t>-29,25; 292,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,86; 146,45</t>
+          <t>-68,51; 118,27</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,66</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-8,93</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>10,88</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,95</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,66</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,63</t>
+          <t>-2,81</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,11</t>
+          <t>-6,16</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 24,23</t>
+          <t>-10,09; 12,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 16,86</t>
+          <t>-12,45; 10,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 6,03</t>
+          <t>-19,56; -1,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 13,95</t>
+          <t>-2,64; 24,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 11,15</t>
+          <t>-8,58; 18,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,31; -1,06</t>
+          <t>-15,43; 6,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 16,13</t>
+          <t>-3,61; 14,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 10,67</t>
+          <t>-7,51; 10,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 0,44</t>
+          <t>-14,7; -0,27</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19,77%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-15,45%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-82,94%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>128,51%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>51,66%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-34,82%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>19,77%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-15,45%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-80,14%</t>
+          <t>-33,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-62,0%</t>
+          <t>-62,52%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,43; 881,12</t>
+          <t>-59,04; 261,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-73,13; 649,23</t>
+          <t>-83,51; 207,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 112,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 248,2</t>
+          <t>-28,15; inf</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-81,76; 253,81</t>
+          <t>-72,94; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 304,85</t>
+          <t>-27,43; 248,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 234,1</t>
+          <t>-56,5; 191,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-92,6; 21,12</t>
+          <t>-91,19; 23,31</t>
         </is>
       </c>
     </row>
@@ -1488,47 +1488,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,75</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,82</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-4,79</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>8,95</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,78</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-0,57</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5,73</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>2,75</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,82</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,73</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>-2,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 15,47</t>
+          <t>-2,92; 8,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 8,14</t>
+          <t>-3,61; 9,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 5,85</t>
+          <t>-9,84; 0,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 9,2</t>
+          <t>2,11; 16,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 9,41</t>
+          <t>-3,3; 8,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,03; -0,02</t>
+          <t>-5,9; 4,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 10,31</t>
+          <t>1,44; 10,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 7,08</t>
+          <t>-1,81; 7,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 1,12</t>
+          <t>-6,46; 0,75</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>26,99%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>27,68%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-46,91%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>100,58%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>31,27%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-5,1%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-47,29%</t>
+          <t>-6,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-28,17%</t>
+          <t>-29,46%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19,25; 250,74</t>
+          <t>-24,3; 118,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,27; 129,42</t>
+          <t>-28,1; 122,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,12; 90,58</t>
+          <t>-74,88; 12,87</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 117,09</t>
+          <t>16,17; 285,28</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 122,51</t>
+          <t>-30,36; 135,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-75,81; 3,34</t>
+          <t>-50,1; 81,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,04; 139,79</t>
+          <t>12,21; 140,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 88,27</t>
+          <t>-15,71; 93,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-57,68; 17,04</t>
+          <t>-55,67; 12,39</t>
         </is>
       </c>
     </row>
